--- a/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/exports/North_Carolina_Surplus_Feed.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:40</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:40</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:40</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:40</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:40</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>

--- a/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/exports/North_Carolina_Surplus_Feed.xlsx
@@ -557,7 +557,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Vacant Land / Acreage</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -582,11 +582,11 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>315</v>
+        <v>0</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -674,11 +674,11 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>308</v>
+        <v>0</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Vacant Land / Acreage</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -766,11 +766,11 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>329</v>
+        <v>0</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -858,11 +858,11 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>322</v>
+        <v>0</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -950,11 +950,11 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>301</v>
+        <v>0</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>

--- a/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/exports/North_Carolina_Surplus_Feed.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,106 +425,116 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T6"/>
+  <dimension ref="A1:V6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>County</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Case_or_TaxDeed_No</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Owner_Name</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Entity_Type</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Is_Individual</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Heir_Search_Recommended</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Property_Address</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Property_Type</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Surplus_Balance_USD</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Statutory_Fee_Rate</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Est_Finder_Fee_USD</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Opportunity_Tier</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Sale_Date</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Days_Remaining_To_Claim</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Claim_Urgency_Tier</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Claim_Deadline_Date</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Statutory_Deadline_Window</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Clerk_Verification_URL</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Governing_Statute</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Statute_Citation</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Enriched_Timestamp</t>
         </is>
@@ -582,31 +604,41 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>10-Day Upset Bid / Judicial Registry (N.C.G.S. § 105-374)</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>https://www.nccourts.gov/locations/mecklenburg</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>N.C.G.S. § 105-374</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>N.C.G.S. § 105-374</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -674,31 +706,41 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>10-Day Upset Bid / Judicial Registry (N.C.G.S. § 105-374)</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>https://www.nccourts.gov/locations/wake</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>N.C.G.S. § 105-374</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>N.C.G.S. § 105-374</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -766,31 +808,41 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>10-Day Upset Bid / Judicial Registry (N.C.G.S. § 105-374)</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>https://www.nccourts.gov/locations/mecklenburg</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>N.C.G.S. § 105-374</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>N.C.G.S. § 105-374</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -858,31 +910,41 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>10-Day Upset Bid / Judicial Registry (N.C.G.S. § 105-374)</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>https://www.nccourts.gov/locations/wake</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>N.C.G.S. § 105-374</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>N.C.G.S. § 105-374</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -950,31 +1012,41 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
           <t>10-Day Upset Bid / Judicial Registry (N.C.G.S. § 105-374)</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>https://www.nccourts.gov/locations/durham</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>N.C.G.S. § 105-374</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>N.C.G.S. § 105-374</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>

--- a/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/exports/North_Carolina_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>

--- a/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/exports/North_Carolina_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>

--- a/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/exports/North_Carolina_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>

--- a/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/exports/North_Carolina_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>

--- a/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/exports/North_Carolina_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>

--- a/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/exports/North_Carolina_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>

--- a/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/exports/North_Carolina_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>

--- a/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/exports/North_Carolina_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>

--- a/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/exports/North_Carolina_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>

--- a/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/exports/North_Carolina_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>

--- a/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/exports/North_Carolina_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>

--- a/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/exports/North_Carolina_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>

--- a/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/exports/North_Carolina_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>

--- a/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/exports/North_Carolina_Surplus_Feed.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:Y6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,100 +441,115 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Parcel_ID</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Case_or_TaxDeed_No</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Owner_Name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Entity_Type</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Is_Individual</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Heir_Search_Recommended</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Property_Address</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Property_Type</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Surplus_Balance_USD</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Statutory_Fee_Rate</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Est_Finder_Fee_USD</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Opportunity_Tier</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Sale_Date</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Days_Remaining_To_Claim</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Claim_Urgency_Tier</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Claim_Deadline_Date</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Statutory_Deadline_Window</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Clerk_Verification_URL</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Governing_Statute</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Statute_Citation</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Record_Type</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>TYPE</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Enriched_Timestamp</t>
         </is>
@@ -553,92 +568,107 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>2024-NC-003110</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>DERRICK &amp; ANGELA MORGAN</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Individual / Estate</t>
         </is>
       </c>
-      <c r="F2" t="b">
+      <c r="G2" t="b">
         <v>1</v>
       </c>
-      <c r="G2" t="b">
+      <c r="H2" t="b">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>5820 SHARON RD CHARLOTTE NC 28210</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>138000</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>27600</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>2024-07-25</t>
         </is>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>50</v>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
       <c r="R2" t="inlineStr">
         <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
           <t>10-Day Upset Bid / Judicial Registry (N.C.G.S. § 105-374)</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>https://www.nccourts.gov/locations/mecklenburg</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>N.C.G.S. § 105-374</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>N.C.G.S. § 105-374</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -655,92 +685,107 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>2024-NC-001420</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>HARRISON &amp; CAROLINE VANCE</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Individual / Estate</t>
         </is>
       </c>
-      <c r="F3" t="b">
+      <c r="G3" t="b">
         <v>1</v>
       </c>
-      <c r="G3" t="b">
+      <c r="H3" t="b">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>4210 GLENWOOD AVE RALEIGH NC 27612</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>114500</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>22900</v>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>2024-07-18</t>
         </is>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>50</v>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
       <c r="R3" t="inlineStr">
         <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
           <t>10-Day Upset Bid / Judicial Registry (N.C.G.S. § 105-374)</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>https://www.nccourts.gov/locations/wake</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>N.C.G.S. § 105-374</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>N.C.G.S. § 105-374</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -757,92 +802,107 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>2024-NC-003450</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>ESTATE OF WALTER STERLING</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Estate / Deceased</t>
         </is>
-      </c>
-      <c r="F4" t="b">
-        <v>1</v>
       </c>
       <c r="G4" t="b">
         <v>1</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>2910 PROVIDENCE RD CHARLOTTE NC 28211</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>96400</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>19280</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>2024-08-08</t>
         </is>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>50</v>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
       <c r="R4" t="inlineStr">
         <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
           <t>10-Day Upset Bid / Judicial Registry (N.C.G.S. § 105-374)</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>https://www.nccourts.gov/locations/mecklenburg</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>N.C.G.S. § 105-374</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>N.C.G.S. § 105-374</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -859,92 +919,107 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>2024-NC-001890</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>ESTATE OF SAMUEL KAUFMAN</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Estate / Deceased</t>
         </is>
-      </c>
-      <c r="F5" t="b">
-        <v>1</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>1804 FALLS OF NEUSE RD RALEIGH NC 27609</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>88200</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>17640</v>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>2024-08-01</t>
         </is>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>50</v>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
       <c r="R5" t="inlineStr">
         <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
           <t>10-Day Upset Bid / Judicial Registry (N.C.G.S. § 105-374)</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>https://www.nccourts.gov/locations/wake</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>N.C.G.S. § 105-374</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>N.C.G.S. § 105-374</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -961,92 +1036,107 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>2024-NC-002100</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>PATRICIA HOLLOWAY</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Individual / Estate</t>
         </is>
       </c>
-      <c r="F6" t="b">
+      <c r="G6" t="b">
         <v>1</v>
       </c>
-      <c r="G6" t="b">
+      <c r="H6" t="b">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>1408 DUKE UNIVERSITY RD DURHAM NC 27701</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>64500</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>12900</v>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>2024-07-11</t>
         </is>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>50</v>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
       <c r="R6" t="inlineStr">
         <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
           <t>10-Day Upset Bid / Judicial Registry (N.C.G.S. § 105-374)</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>https://www.nccourts.gov/locations/durham</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>N.C.G.S. § 105-374</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>N.C.G.S. § 105-374</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>

--- a/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/exports/North_Carolina_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>

--- a/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/exports/North_Carolina_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>

--- a/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/exports/North_Carolina_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>

--- a/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/exports/North_Carolina_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>

--- a/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/exports/North_Carolina_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>

--- a/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/exports/North_Carolina_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>

--- a/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/exports/North_Carolina_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>

--- a/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/exports/North_Carolina_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>

--- a/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/exports/North_Carolina_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>

--- a/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/exports/North_Carolina_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/mecklenburg</t>
+          <t>https://www.nccourts.gov/locations/mecklenburg?docket=2024-NC-003110</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/wake</t>
+          <t>https://www.nccourts.gov/locations/wake/wake-county-clerk-of-superior-court?docket=2024-NC-001420</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/mecklenburg</t>
+          <t>https://www.nccourts.gov/locations/mecklenburg?docket=2024-NC-003450</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/wake</t>
+          <t>https://www.nccourts.gov/locations/wake/wake-county-clerk-of-superior-court?docket=2024-NC-001890</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/durham</t>
+          <t>https://www.nccourts.gov/locations/durham?docket=2024-NC-002100</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>

--- a/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/exports/North_Carolina_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/mecklenburg?docket=2024-NC-003110</t>
+          <t>https://www.nccourts.gov/locations/mecklenburg</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/wake/wake-county-clerk-of-superior-court?docket=2024-NC-001420</t>
+          <t>https://www.nccourts.gov/locations/wake</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/mecklenburg?docket=2024-NC-003450</t>
+          <t>https://www.nccourts.gov/locations/mecklenburg</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/wake/wake-county-clerk-of-superior-court?docket=2024-NC-001890</t>
+          <t>https://www.nccourts.gov/locations/wake</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/durham?docket=2024-NC-002100</t>
+          <t>https://www.nccourts.gov/locations/durham</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>

--- a/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/exports/North_Carolina_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/mecklenburg</t>
+          <t>https://www.nccourts.gov/locations/mecklenburg-county?docket=2024-NC-003110</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/wake</t>
+          <t>https://www.nccourts.gov/locations/wake-county?docket=2024-NC-001420</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/mecklenburg</t>
+          <t>https://www.nccourts.gov/locations/mecklenburg-county?docket=2024-NC-003450</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/wake</t>
+          <t>https://www.nccourts.gov/locations/wake-county?docket=2024-NC-001890</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/durham</t>
+          <t>https://www.nccourts.gov/locations/durham-county?docket=2024-NC-002100</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>

--- a/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/exports/North_Carolina_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>

--- a/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/exports/North_Carolina_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>

--- a/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/exports/North_Carolina_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>

--- a/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/exports/North_Carolina_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>

--- a/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/exports/North_Carolina_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>

--- a/exports/North_Carolina_Surplus_Feed.xlsx
+++ b/exports/North_Carolina_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
